--- a/data/trans_camb/IP2003-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP2003-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 14,7</t>
+          <t>-3,68; 14,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,22; 26,35</t>
+          <t>3,84; 25,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 20,04</t>
+          <t>0,43; 19,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 18,47</t>
+          <t>-4,08; 19,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,37; 1,93</t>
+          <t>-17,47; 2,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 15,41</t>
+          <t>-8,44; 14,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 14,14</t>
+          <t>-1,59; 14,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 11,33</t>
+          <t>-4,36; 10,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 13,71</t>
+          <t>-1,85; 14,52</t>
         </is>
       </c>
     </row>
@@ -783,54 +783,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-43,81; 458,25</t>
+          <t>-39,24; 446,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34,77; 624,88</t>
+          <t>24,98; 699,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 519,69</t>
+          <t>-4,15; 573,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-26,55; 208,86</t>
+          <t>-21,81; 207,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-82,42; 26,23</t>
+          <t>-80,61; 40,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-44,46; 174,06</t>
+          <t>-43,25; 165,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 191,58</t>
+          <t>-12,54; 181,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,5; 140,98</t>
+          <t>-30,36; 124,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-15,79; 166,61</t>
+          <t>-15,24; 185,1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-25,8; -7,0</t>
+          <t>-26,92; -6,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-24,24; -4,98</t>
+          <t>-25,41; -5,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 44,6</t>
+          <t>-2,06; 44,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-21,86; -5,21</t>
+          <t>-21,99; -6,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,52; 5,38</t>
+          <t>-12,74; 4,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 16,5</t>
+          <t>-6,96; 16,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-21,9; -9,49</t>
+          <t>-21,7; -9,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-16,51; -2,71</t>
+          <t>-16,06; -2,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 29,2</t>
+          <t>-0,42; 31,62</t>
         </is>
       </c>
     </row>
@@ -999,54 +999,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-73,64; -28,52</t>
+          <t>-74,23; -26,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-70,7; -20,29</t>
+          <t>-70,73; -19,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 169,15</t>
+          <t>-7,51; 184,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-75,48; -26,22</t>
+          <t>-76,32; -29,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-46,38; 29,23</t>
+          <t>-45,75; 25,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,56; 89,63</t>
+          <t>-25,02; 84,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-70,03; -38,4</t>
+          <t>-71,34; -37,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-54,25; -11,37</t>
+          <t>-52,53; -9,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 128,5</t>
+          <t>-1,67; 123,02</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-16,3; 3,21</t>
+          <t>-15,19; 4,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,83; 1,29</t>
+          <t>-18,77; 0,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,7; -0,3</t>
+          <t>-18,48; 0,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 9,33</t>
+          <t>-7,19; 9,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,88; 3,44</t>
+          <t>-12,15; 2,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 6,53</t>
+          <t>-9,57; 6,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 3,64</t>
+          <t>-9,52; 3,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-13,52; -1,19</t>
+          <t>-12,93; -0,67</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 0,62</t>
+          <t>-11,89; 0,31</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-73,96; 38,15</t>
+          <t>-73,64; 50,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-87,31; 24,73</t>
+          <t>-89,71; 20,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-85,77; 2,93</t>
+          <t>-82,75; 14,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-53,44; 134,3</t>
+          <t>-54,36; 151,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-82,87; 72,89</t>
+          <t>-85,26; 66,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-67,93; 119,52</t>
+          <t>-68,63; 125,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-55,73; 41,66</t>
+          <t>-57,19; 39,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-79,39; -4,09</t>
+          <t>-76,81; -0,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-68,9; 9,43</t>
+          <t>-72,0; 6,25</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 15,79</t>
+          <t>-6,26; 16,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 18,12</t>
+          <t>-5,68; 18,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,97; 4,57</t>
+          <t>-18,45; 3,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 10,8</t>
+          <t>-7,94; 10,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,61; 21,8</t>
+          <t>2,03; 22,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 48,2</t>
+          <t>-3,93; 46,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 9,65</t>
+          <t>-3,98; 9,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,82; 17,06</t>
+          <t>1,31; 16,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 23,39</t>
+          <t>-7,06; 21,93</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-28,53; 110,79</t>
+          <t>-24,67; 116,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-19,0; 125,21</t>
+          <t>-23,58; 131,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-71,03; 36,01</t>
+          <t>-73,99; 21,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-44,52; 144,19</t>
+          <t>-51,25; 143,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,08; 296,51</t>
+          <t>2,58; 284,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-34,03; 701,47</t>
+          <t>-37,17; 581,23</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-20,94; 84,48</t>
+          <t>-21,71; 82,62</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,67; 136,71</t>
+          <t>3,6; 132,32</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-41,16; 179,44</t>
+          <t>-41,92; 168,56</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-16,39; 15,96</t>
+          <t>-15,87; 15,61</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-31,34; -4,38</t>
+          <t>-30,54; -4,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-31,0; -5,08</t>
+          <t>-31,92; -5,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 16,73</t>
+          <t>-10,77; 17,94</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-15,28; 10,67</t>
+          <t>-14,36; 11,42</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-18,06; 6,51</t>
+          <t>-19,39; 5,73</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-9,68; 11,55</t>
+          <t>-9,35; 12,04</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-18,41; 0,07</t>
+          <t>-19,66; 0,9</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-20,9; -2,42</t>
+          <t>-20,93; -3,35</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-47,97; 92,98</t>
+          <t>-47,74; 92,75</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-89,85; -12,47</t>
+          <t>-90,22; -21,19</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-87,95; -24,7</t>
+          <t>-90,47; -26,83</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-48,47; 148,72</t>
+          <t>-47,8; 186,11</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-65,05; 93,49</t>
+          <t>-58,01; 110,23</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-73,4; 64,93</t>
+          <t>-76,23; 55,03</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-35,67; 68,84</t>
+          <t>-34,64; 68,85</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-69,05; 4,27</t>
+          <t>-71,35; 7,93</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-75,77; -11,36</t>
+          <t>-78,29; -18,4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 22,59</t>
+          <t>-3,13; 21,32</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-13,24; 9,67</t>
+          <t>-13,52; 8,92</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-18,45; -0,6</t>
+          <t>-17,86; -0,47</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3,06; 23,1</t>
+          <t>3,69; 23,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 14,79</t>
+          <t>-3,27; 14,3</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 6,92</t>
+          <t>-6,72; 6,11</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,3; 18,37</t>
+          <t>3,61; 18,55</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 9,12</t>
+          <t>-4,92; 8,46</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 0,86</t>
+          <t>-10,15; 0,84</t>
         </is>
       </c>
     </row>
@@ -1863,54 +1863,54 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-13,68; 294,57</t>
+          <t>-22,77; 270,82</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-74,23; 128,36</t>
+          <t>-75,72; 122,55</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-93,81; 6,31</t>
+          <t>-93,61; 30,85</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6,12; 947,85</t>
+          <t>18,73; 1007,48</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-53,81; 669,83</t>
+          <t>-49,7; 616,19</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-84,88; 456,65</t>
+          <t>-85,43; 304,82</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>22,39; 298,55</t>
+          <t>25,53; 294,63</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-42,97; 145,54</t>
+          <t>-43,81; 139,87</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-84,02; 21,43</t>
+          <t>-82,57; 24,29</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 10,3</t>
+          <t>-4,97; 10,12</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 2,11</t>
+          <t>-10,86; 1,35</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 9,77</t>
+          <t>-4,76; 9,69</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 6,76</t>
+          <t>-5,57; 6,85</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 5,32</t>
+          <t>-6,53; 4,87</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 9,91</t>
+          <t>-2,38; 10,64</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 7,26</t>
+          <t>-2,6; 6,91</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 1,99</t>
+          <t>-6,63; 1,99</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 7,93</t>
+          <t>-1,72; 7,81</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-29,01; 119,72</t>
+          <t>-33,79; 123,78</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-68,12; 29,08</t>
+          <t>-69,54; 20,98</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-32,4; 114,39</t>
+          <t>-31,05; 116,65</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-45,57; 99,05</t>
+          <t>-44,76; 98,07</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-54,93; 85,4</t>
+          <t>-53,42; 72,06</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-33,13; 146,34</t>
+          <t>-21,67; 155,3</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-19,45; 93,33</t>
+          <t>-20,09; 82,65</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-52,38; 26,14</t>
+          <t>-52,0; 25,22</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-17,13; 97,02</t>
+          <t>-16,05; 94,17</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 7,28</t>
+          <t>-6,37; 7,37</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 3,11</t>
+          <t>-9,91; 2,92</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-17,65; -5,64</t>
+          <t>-16,87; -5,76</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 1,5</t>
+          <t>-10,95; 1,23</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 1,73</t>
+          <t>-10,28; 1,72</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-17,84; -6,71</t>
+          <t>-17,32; -6,58</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 2,11</t>
+          <t>-6,85; 2,08</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 0,59</t>
+          <t>-8,82; 0,37</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-15,87; -7,91</t>
+          <t>-16,13; -8,45</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-33,44; 54,38</t>
+          <t>-33,33; 61,76</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-52,34; 25,33</t>
+          <t>-51,48; 24,84</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-86,13; -38,31</t>
+          <t>-85,98; -41,66</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-56,01; 12,3</t>
+          <t>-55,87; 11,73</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-56,05; 14,62</t>
+          <t>-53,02; 13,91</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-91,92; -47,54</t>
+          <t>-90,09; -44,05</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-35,11; 17,02</t>
+          <t>-36,77; 15,51</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-45,22; 4,83</t>
+          <t>-46,16; 2,62</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-84,76; -54,21</t>
+          <t>-84,79; -55,77</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 2,52</t>
+          <t>-4,03; 2,6</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-7,21; -0,84</t>
+          <t>-6,83; -0,91</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 12,81</t>
+          <t>-5,34; 11,46</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 2,14</t>
+          <t>-4,37; 1,69</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 1,46</t>
+          <t>-4,07; 1,9</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 4,84</t>
+          <t>-3,77; 4,42</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 1,42</t>
+          <t>-3,11; 1,61</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-5,07; -0,36</t>
+          <t>-4,94; -0,52</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 5,8</t>
+          <t>-3,31; 5,31</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-22,17; 15,76</t>
+          <t>-21,07; 16,09</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-38,69; -5,21</t>
+          <t>-36,26; -5,29</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-29,52; 87,83</t>
+          <t>-28,94; 72,96</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-25,17; 16,89</t>
+          <t>-27,57; 12,94</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-28,04; 11,82</t>
+          <t>-26,27; 13,91</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-23,7; 39,13</t>
+          <t>-24,52; 33,69</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-19,28; 8,83</t>
+          <t>-18,82; 10,63</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-28,82; -1,89</t>
+          <t>-28,54; -3,38</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-19,52; 37,75</t>
+          <t>-20,26; 37,94</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2003-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP2003-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 14,89</t>
+          <t>-4,18; 13,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,84; 25,7</t>
+          <t>5,57; 26,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 19,85</t>
+          <t>-0,13; 19,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 19,2</t>
+          <t>-5,61; 18,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-17,47; 2,51</t>
+          <t>-17,52; 2,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 14,63</t>
+          <t>-10,0; 14,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 14,54</t>
+          <t>-2,4; 13,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 10,78</t>
+          <t>-4,53; 10,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 14,52</t>
+          <t>-1,79; 14,46</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-39,24; 446,69</t>
+          <t>-45,62; 372,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,98; 699,01</t>
+          <t>30,19; 715,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 573,76</t>
+          <t>-7,8; 565,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-21,81; 207,47</t>
+          <t>-27,82; 226,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-80,61; 40,88</t>
+          <t>-81,25; 37,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-43,25; 165,14</t>
+          <t>-46,21; 151,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-12,54; 181,67</t>
+          <t>-16,54; 175,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-30,36; 124,47</t>
+          <t>-29,9; 138,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-15,24; 185,1</t>
+          <t>-13,65; 177,23</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-26,92; -6,69</t>
+          <t>-26,22; -7,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-25,41; -5,03</t>
+          <t>-25,0; -5,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 44,32</t>
+          <t>-1,05; 45,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-21,99; -6,1</t>
+          <t>-21,85; -5,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,74; 4,67</t>
+          <t>-13,2; 5,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 16,54</t>
+          <t>-7,89; 15,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-21,7; -9,25</t>
+          <t>-21,02; -8,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-16,06; -2,5</t>
+          <t>-16,12; -2,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 31,62</t>
+          <t>-1,26; 27,72</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-74,23; -26,4</t>
+          <t>-74,75; -29,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-70,73; -19,9</t>
+          <t>-70,36; -20,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 184,51</t>
+          <t>-4,19; 210,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-76,32; -29,9</t>
+          <t>-76,25; -29,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-45,75; 25,06</t>
+          <t>-46,67; 28,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,02; 84,24</t>
+          <t>-29,01; 79,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-71,34; -37,76</t>
+          <t>-69,82; -35,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-52,53; -9,8</t>
+          <t>-53,12; -10,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 123,02</t>
+          <t>-5,0; 122,22</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,19; 4,27</t>
+          <t>-15,43; 3,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,77; 0,68</t>
+          <t>-18,17; 1,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,48; 0,63</t>
+          <t>-18,0; -0,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 9,37</t>
+          <t>-7,29; 9,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 2,91</t>
+          <t>-12,36; 2,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 6,91</t>
+          <t>-9,43; 7,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 3,72</t>
+          <t>-9,13; 3,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,93; -0,67</t>
+          <t>-12,29; -0,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 0,31</t>
+          <t>-11,12; 0,7</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-73,64; 50,6</t>
+          <t>-73,43; 44,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-89,71; 20,89</t>
+          <t>-86,95; 16,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-82,75; 14,76</t>
+          <t>-82,38; 8,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-54,36; 151,71</t>
+          <t>-55,46; 134,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-85,26; 66,29</t>
+          <t>-86,37; 57,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-68,63; 125,05</t>
+          <t>-70,33; 130,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-57,19; 39,73</t>
+          <t>-55,23; 35,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-76,81; -0,08</t>
+          <t>-77,38; -1,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-72,0; 6,25</t>
+          <t>-68,68; 10,31</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 16,91</t>
+          <t>-6,04; 16,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 18,86</t>
+          <t>-5,23; 18,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,45; 3,0</t>
+          <t>-17,66; 3,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 10,5</t>
+          <t>-7,11; 10,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,03; 22,71</t>
+          <t>1,05; 21,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 46,0</t>
+          <t>-4,91; 42,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 9,98</t>
+          <t>-3,55; 10,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 16,87</t>
+          <t>1,3; 16,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 21,93</t>
+          <t>-7,03; 24,07</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-24,67; 116,07</t>
+          <t>-26,71; 118,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-23,58; 131,04</t>
+          <t>-23,97; 121,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-73,99; 21,22</t>
+          <t>-73,49; 24,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-51,25; 143,17</t>
+          <t>-44,43; 131,16</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,58; 284,19</t>
+          <t>5,78; 279,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-37,17; 581,23</t>
+          <t>-38,8; 563,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-21,71; 82,62</t>
+          <t>-18,59; 83,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,6; 132,32</t>
+          <t>6,98; 143,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-41,92; 168,56</t>
+          <t>-42,76; 194,7</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-15,87; 15,61</t>
+          <t>-16,46; 15,89</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-30,54; -4,53</t>
+          <t>-31,85; -4,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-31,92; -5,29</t>
+          <t>-30,22; -4,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 17,94</t>
+          <t>-12,38; 15,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-14,36; 11,42</t>
+          <t>-14,25; 11,15</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-19,39; 5,73</t>
+          <t>-18,06; 5,97</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 12,04</t>
+          <t>-9,15; 11,69</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-19,66; 0,9</t>
+          <t>-18,42; -0,01</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-20,93; -3,35</t>
+          <t>-20,2; -2,49</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-47,74; 92,75</t>
+          <t>-49,52; 85,56</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-90,22; -21,19</t>
+          <t>-90,05; -17,84</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-90,47; -26,83</t>
+          <t>-88,11; -20,59</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-47,8; 186,11</t>
+          <t>-48,47; 130,26</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-58,01; 110,23</t>
+          <t>-59,39; 98,07</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-76,23; 55,03</t>
+          <t>-74,49; 59,65</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-34,64; 68,85</t>
+          <t>-34,24; 74,71</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-71,35; 7,93</t>
+          <t>-69,32; 1,95</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-78,29; -18,4</t>
+          <t>-74,11; -11,7</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 21,32</t>
+          <t>-3,13; 22,06</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-13,52; 8,92</t>
+          <t>-12,59; 9,2</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-17,86; -0,47</t>
+          <t>-18,5; -1,33</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3,69; 23,0</t>
+          <t>2,76; 21,55</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 14,3</t>
+          <t>-2,7; 13,83</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 6,11</t>
+          <t>-7,46; 5,39</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,61; 18,55</t>
+          <t>2,88; 19,25</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 8,46</t>
+          <t>-5,48; 8,62</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 0,84</t>
+          <t>-10,51; 0,65</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-22,77; 270,82</t>
+          <t>-21,28; 280,15</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-75,72; 122,55</t>
+          <t>-73,05; 132,64</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-93,61; 30,85</t>
+          <t>-93,6; 8,61</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>18,73; 1007,48</t>
+          <t>13,78; 867,2</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-49,7; 616,19</t>
+          <t>-44,28; 659,89</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-85,43; 304,82</t>
+          <t>-88,53; 338,95</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>25,53; 294,63</t>
+          <t>18,71; 319,28</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-43,81; 139,87</t>
+          <t>-44,94; 145,66</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-82,57; 24,29</t>
+          <t>-83,71; 14,94</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 10,12</t>
+          <t>-4,1; 10,7</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-10,86; 1,35</t>
+          <t>-10,64; 1,27</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 9,69</t>
+          <t>-4,43; 10,06</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 6,85</t>
+          <t>-5,33; 6,75</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 4,87</t>
+          <t>-6,67; 5,15</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 10,64</t>
+          <t>-3,58; 9,5</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 6,91</t>
+          <t>-2,52; 6,76</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 1,99</t>
+          <t>-6,65; 2,03</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 7,81</t>
+          <t>-2,06; 7,6</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-33,79; 123,78</t>
+          <t>-28,0; 119,81</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-69,54; 20,98</t>
+          <t>-72,13; 17,98</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-31,05; 116,65</t>
+          <t>-31,87; 121,88</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-44,76; 98,07</t>
+          <t>-44,13; 115,61</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-53,42; 72,06</t>
+          <t>-54,83; 78,81</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-21,67; 155,3</t>
+          <t>-32,31; 159,21</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-20,09; 82,65</t>
+          <t>-20,09; 79,24</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-52,0; 25,22</t>
+          <t>-53,26; 26,68</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-16,05; 94,17</t>
+          <t>-16,2; 93,49</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 7,37</t>
+          <t>-6,31; 7,08</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 2,92</t>
+          <t>-9,98; 2,91</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-16,87; -5,76</t>
+          <t>-17,42; -5,8</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 1,23</t>
+          <t>-10,65; 1,48</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 1,72</t>
+          <t>-10,57; 1,96</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-17,32; -6,58</t>
+          <t>-17,22; -6,91</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 2,08</t>
+          <t>-7,36; 2,08</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 0,37</t>
+          <t>-8,74; 0,27</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-16,13; -8,45</t>
+          <t>-16,03; -8,38</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-33,33; 61,76</t>
+          <t>-33,04; 58,8</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-51,48; 24,84</t>
+          <t>-51,77; 25,65</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-85,98; -41,66</t>
+          <t>-85,98; -42,13</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-55,87; 11,73</t>
+          <t>-55,8; 13,62</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-53,02; 13,91</t>
+          <t>-55,47; 13,4</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-90,09; -44,05</t>
+          <t>-90,69; -50,04</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-36,77; 15,51</t>
+          <t>-38,91; 14,28</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-46,16; 2,62</t>
+          <t>-46,61; 1,72</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-84,79; -55,77</t>
+          <t>-84,53; -57,11</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 2,6</t>
+          <t>-4,01; 3,06</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-6,83; -0,91</t>
+          <t>-7,21; -0,38</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 11,46</t>
+          <t>-5,4; 10,66</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 1,69</t>
+          <t>-3,82; 2,03</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 1,9</t>
+          <t>-4,34; 1,86</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 4,42</t>
+          <t>-3,83; 4,88</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 1,61</t>
+          <t>-3,09; 1,32</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-4,94; -0,52</t>
+          <t>-4,66; -0,26</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 5,31</t>
+          <t>-3,31; 6,28</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-21,07; 16,09</t>
+          <t>-20,73; 19,6</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-36,26; -5,29</t>
+          <t>-37,41; -2,12</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-28,94; 72,96</t>
+          <t>-29,22; 75,68</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-27,57; 12,94</t>
+          <t>-24,35; 16,78</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-26,27; 13,91</t>
+          <t>-27,87; 14,58</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-24,52; 33,69</t>
+          <t>-25,47; 35,92</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-18,82; 10,63</t>
+          <t>-18,07; 9,02</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-28,54; -3,38</t>
+          <t>-27,82; -1,92</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-20,26; 37,94</t>
+          <t>-20,18; 41,37</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2003-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP2003-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7,08</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-7,45</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,64</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>4,75</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>15,34</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9,95</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7,08</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-7,45</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,57</t>
+          <t>13,61</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6,04</t>
+          <t>7,3</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 13,72</t>
+          <t>-5,64; 18,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,57; 26,25</t>
+          <t>-18,37; 1,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 19,87</t>
+          <t>-9,87; 13,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 18,62</t>
+          <t>-4,18; 14,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-17,52; 2,62</t>
+          <t>5,22; 26,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 14,08</t>
+          <t>4,69; 23,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 13,35</t>
+          <t>-1,54; 14,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 10,48</t>
+          <t>-3,75; 11,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 14,46</t>
+          <t>-0,52; 15,31</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>45,96%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-48,42%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10,68%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>63,3%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>204,5%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>132,62%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>45,96%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-48,42%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>181,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>62,54%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-45,62; 372,56</t>
+          <t>-26,55; 208,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,19; 715,92</t>
+          <t>-82,42; 26,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 565,96</t>
+          <t>-45,77; 163,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,82; 226,86</t>
+          <t>-43,81; 458,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-81,25; 37,58</t>
+          <t>34,77; 624,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-46,21; 151,07</t>
+          <t>24,63; 643,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,54; 175,27</t>
+          <t>-10,84; 191,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,9; 138,61</t>
+          <t>-28,5; 140,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-13,65; 177,23</t>
+          <t>-3,98; 191,23</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-13,9</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-4,27</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3,93</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-16,93</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-15,29</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>17,08</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-13,9</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-4,27</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,53</t>
+          <t>3,71</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10,5</t>
+          <t>3,79</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-26,22; -7,78</t>
+          <t>-21,86; -5,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-25,0; -5,59</t>
+          <t>-13,52; 5,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 45,75</t>
+          <t>-6,95; 16,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-21,85; -5,85</t>
+          <t>-25,8; -7,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 5,17</t>
+          <t>-24,24; -4,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 15,75</t>
+          <t>-7,25; 14,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-21,02; -8,45</t>
+          <t>-21,9; -9,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-16,12; -2,45</t>
+          <t>-16,51; -2,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 27,72</t>
+          <t>-5,16; 11,81</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-57,28%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-17,59%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16,19%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-55,92%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-50,49%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>56,4%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-57,28%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-17,59%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-74,75; -29,82</t>
+          <t>-75,48; -26,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-70,36; -20,12</t>
+          <t>-46,38; 29,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 210,51</t>
+          <t>-26,1; 87,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-76,25; -29,12</t>
+          <t>-73,64; -28,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-46,67; 28,36</t>
+          <t>-70,7; -20,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,01; 79,47</t>
+          <t>-20,5; 58,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-69,82; -35,46</t>
+          <t>-70,03; -38,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-53,12; -10,39</t>
+          <t>-54,25; -11,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 122,22</t>
+          <t>-17,39; 49,69</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,59</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-4,69</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-1,66</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-6,12</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-9,0</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-8,92</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,59</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-4,69</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,63</t>
+          <t>-8,71</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-5,16</t>
+          <t>-5,11</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,43; 3,77</t>
+          <t>-7,16; 9,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,17; 1,11</t>
+          <t>-11,88; 3,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,0; -0,28</t>
+          <t>-9,46; 6,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 9,18</t>
+          <t>-16,3; 3,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,36; 2,64</t>
+          <t>-18,83; 1,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 7,48</t>
+          <t>-18,18; 0,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 3,54</t>
+          <t>-8,87; 3,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,29; -0,71</t>
+          <t>-13,52; -1,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 0,7</t>
+          <t>-11,18; 0,8</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5,72%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-45,5%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-16,09%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-38,36%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-56,42%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-55,87%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5,72%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-45,5%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-15,83%</t>
+          <t>-54,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-39,45%</t>
+          <t>-39,09%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-73,43; 44,47</t>
+          <t>-53,44; 134,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-86,95; 16,99</t>
+          <t>-82,87; 72,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-82,38; 8,35</t>
+          <t>-68,02; 119,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-55,46; 134,35</t>
+          <t>-73,96; 38,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-86,37; 57,8</t>
+          <t>-87,31; 24,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-70,33; 130,9</t>
+          <t>-85,12; 7,85</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-55,23; 35,88</t>
+          <t>-55,73; 41,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-77,38; -1,6</t>
+          <t>-79,39; -4,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-68,68; 10,31</t>
+          <t>-68,56; 9,68</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11,09</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>10,84</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>4,72</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>7,0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-7,61</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,6</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>11,09</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,32</t>
+          <t>-7,3</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,76</t>
+          <t>1,91</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 16,55</t>
+          <t>-7,02; 10,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 18,83</t>
+          <t>1,61; 21,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,66; 3,32</t>
+          <t>-3,87; 43,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 10,47</t>
+          <t>-6,77; 15,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 21,11</t>
+          <t>-4,66; 18,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 42,77</t>
+          <t>-17,86; 4,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 10,45</t>
+          <t>-3,71; 9,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 16,59</t>
+          <t>1,82; 17,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 24,07</t>
+          <t>-7,05; 19,36</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>13,37%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>92,75%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>90,69%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>23,83%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>35,34%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-38,42%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>13,37%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>92,75%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>103,05%</t>
+          <t>-36,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-26,71; 118,96</t>
+          <t>-44,52; 144,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-23,97; 121,83</t>
+          <t>2,08; 296,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-73,49; 24,83</t>
+          <t>-35,22; 617,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-44,43; 131,16</t>
+          <t>-28,53; 110,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,78; 279,95</t>
+          <t>-19,0; 125,21</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-38,8; 563,38</t>
+          <t>-70,43; 36,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-18,59; 83,28</t>
+          <t>-20,94; 84,48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,98; 143,51</t>
+          <t>8,67; 136,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-42,76; 194,7</t>
+          <t>-42,16; 150,52</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2,29</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,47</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-5,55</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-0,51</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-17,74</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-18,08</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2,29</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-1,47</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-5,96</t>
+          <t>-18,07</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-11,69</t>
+          <t>-11,54</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-16,46; 15,89</t>
+          <t>-11,62; 16,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-31,85; -4,68</t>
+          <t>-15,28; 10,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-30,22; -4,07</t>
+          <t>-17,87; 6,98</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-12,38; 15,22</t>
+          <t>-16,39; 15,96</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-14,25; 11,15</t>
+          <t>-31,34; -4,38</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-18,06; 5,97</t>
+          <t>-31,01; -4,93</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 11,69</t>
+          <t>-9,68; 11,55</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-18,42; -0,01</t>
+          <t>-18,41; 0,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-20,2; -2,49</t>
+          <t>-20,86; -2,38</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>12,45%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-7,98%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-30,09%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-1,99%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-68,59%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-69,89%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>12,45%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-7,98%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-32,35%</t>
+          <t>-69,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-53,08%</t>
+          <t>-52,39%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-49,52; 85,56</t>
+          <t>-48,47; 148,72</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-90,05; -17,84</t>
+          <t>-65,05; 93,49</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-88,11; -20,59</t>
+          <t>-72,21; 69,69</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-48,47; 130,26</t>
+          <t>-47,97; 92,98</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-59,39; 98,07</t>
+          <t>-89,85; -12,47</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-74,49; 59,65</t>
+          <t>-87,97; -23,78</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-34,24; 74,71</t>
+          <t>-35,67; 68,84</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-69,32; 1,95</t>
+          <t>-69,05; 4,27</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-74,11; -11,7</t>
+          <t>-75,37; -9,81</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>11,5</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>4,72</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-0,79</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>9,81</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-1,98</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-9,05</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>11,5</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>4,72</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-0,64</t>
+          <t>-8,85</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 22,06</t>
+          <t>3,06; 23,1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 9,2</t>
+          <t>-3,04; 14,79</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-18,5; -1,33</t>
+          <t>-6,78; 6,74</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,76; 21,55</t>
+          <t>-1,87; 22,59</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 13,83</t>
+          <t>-13,24; 9,67</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 5,39</t>
+          <t>-18,44; -0,42</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,88; 19,25</t>
+          <t>3,3; 18,37</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 8,62</t>
+          <t>-5,15; 9,12</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 0,65</t>
+          <t>-10,12; 0,85</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>211,29%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>86,79%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-14,43%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>74,44%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-14,99%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-68,64%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>211,29%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>86,79%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-11,68%</t>
+          <t>-67,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-50,93%</t>
+          <t>-51,0%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-21,28; 280,15</t>
+          <t>6,12; 947,85</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-73,05; 132,64</t>
+          <t>-53,81; 669,83</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-93,6; 8,61</t>
+          <t>-87,94; 439,39</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>13,78; 867,2</t>
+          <t>-13,68; 294,57</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-44,28; 659,89</t>
+          <t>-74,23; 128,36</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-88,53; 338,95</t>
+          <t>-92,98; 11,72</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>18,71; 319,28</t>
+          <t>22,39; 298,55</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-44,94; 145,66</t>
+          <t>-42,97; 145,54</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-83,71; 14,94</t>
+          <t>-84,08; 20,96</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>0,86</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-0,42</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>3,72</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>3,35</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-4,33</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>2,5</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>0,86</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-0,42</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,15</t>
+          <t>3,22</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2,73</t>
+          <t>3,41</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 10,7</t>
+          <t>-5,38; 6,76</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 1,27</t>
+          <t>-6,77; 5,32</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 10,06</t>
+          <t>-3,12; 10,53</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 6,75</t>
+          <t>-4,27; 10,3</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 5,15</t>
+          <t>-10,49; 2,11</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 9,5</t>
+          <t>-4,09; 11,01</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 6,76</t>
+          <t>-2,45; 7,26</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 2,03</t>
+          <t>-6,73; 1,99</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 7,6</t>
+          <t>-1,46; 8,72</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>9,33%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-4,6%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>40,3%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>28,26%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-36,48%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>21,03%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>9,33%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-4,6%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>32,36%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-28,0; 119,81</t>
+          <t>-45,57; 99,05</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-72,13; 17,98</t>
+          <t>-54,93; 85,4</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-31,87; 121,88</t>
+          <t>-28,93; 156,35</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-44,13; 115,61</t>
+          <t>-29,01; 119,72</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-54,83; 78,81</t>
+          <t>-68,12; 29,08</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-32,31; 159,21</t>
+          <t>-26,09; 132,15</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-20,09; 79,24</t>
+          <t>-19,45; 93,33</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-53,26; 26,68</t>
+          <t>-52,38; 26,14</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-16,2; 93,49</t>
+          <t>-11,66; 103,63</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-4,62</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-4,32</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-12,29</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>0,2</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>-3,68</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-11,67</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-4,62</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-4,32</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-12,09</t>
+          <t>-11,99</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-11,92</t>
+          <t>-12,16</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 7,08</t>
+          <t>-10,36; 1,5</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 2,91</t>
+          <t>-10,67; 1,73</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-17,42; -5,8</t>
+          <t>-17,81; -6,99</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-10,65; 1,48</t>
+          <t>-6,99; 7,28</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-10,57; 1,96</t>
+          <t>-10,2; 3,11</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-17,22; -6,91</t>
+          <t>-17,97; -6,14</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 2,08</t>
+          <t>-6,52; 2,11</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 0,27</t>
+          <t>-8,52; 0,59</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-16,03; -8,38</t>
+          <t>-16,05; -8,23</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-28,9%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-27,02%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-76,89%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>1,23%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>-22,39%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-71,07%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-28,9%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>-27,02%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-75,67%</t>
+          <t>-73,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-73,57%</t>
+          <t>-75,06%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-33,04; 58,8</t>
+          <t>-56,01; 12,3</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-51,77; 25,65</t>
+          <t>-56,05; 14,62</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-85,98; -42,13</t>
+          <t>-92,05; -48,65</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-55,8; 13,62</t>
+          <t>-33,44; 54,38</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-55,47; 13,4</t>
+          <t>-52,34; 25,33</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-90,69; -50,04</t>
+          <t>-87,38; -41,85</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-38,91; 14,28</t>
+          <t>-35,11; 17,02</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-46,61; 1,72</t>
+          <t>-45,22; 4,83</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-84,53; -57,11</t>
+          <t>-85,8; -55,61</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-1,05</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-1,27</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>-0,47</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>-0,79</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>-4,06</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-0,33</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-1,05</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-1,27</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-0,14</t>
+          <t>-3,46</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>-1,92</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 3,06</t>
+          <t>-3,85; 2,14</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-7,21; -0,38</t>
+          <t>-4,39; 1,46</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 10,66</t>
+          <t>-3,82; 4,34</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 2,03</t>
+          <t>-4,18; 2,52</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 1,86</t>
+          <t>-7,21; -0,84</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 4,88</t>
+          <t>-7,09; 0,33</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 1,32</t>
+          <t>-3,22; 1,42</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-4,66; -0,26</t>
+          <t>-5,07; -0,36</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 6,28</t>
+          <t>-4,34; 0,86</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-7,37%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-8,93%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>-3,3%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>-4,47%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>-23,1%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-1,9%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-7,37%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-8,93%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-1,02%</t>
+          <t>-19,69%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-1,84%</t>
+          <t>-12,13%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-20,73; 19,6</t>
+          <t>-25,17; 16,89</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-37,41; -2,12</t>
+          <t>-28,04; 11,82</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-29,22; 75,68</t>
+          <t>-24,67; 35,03</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-24,35; 16,78</t>
+          <t>-22,17; 15,76</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-27,87; 14,58</t>
+          <t>-38,69; -5,21</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-25,47; 35,92</t>
+          <t>-35,94; 2,52</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-18,07; 9,02</t>
+          <t>-19,28; 8,83</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-27,82; -1,92</t>
+          <t>-28,82; -1,89</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-20,18; 41,37</t>
+          <t>-25,61; 6,02</t>
         </is>
       </c>
     </row>
